--- a/all_sim/gpt_realset.xlsx
+++ b/all_sim/gpt_realset.xlsx
@@ -331,15 +331,15 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
     <col width="17.6" min="1" max="1" bestFit="1" customWidth="1"/>
-    <col width="24.200000000000003" min="2" max="2" bestFit="1" customWidth="1"/>
-    <col width="24.200000000000003" min="3" max="3" bestFit="1" customWidth="1"/>
+    <col width="23.1" min="2" max="2" bestFit="1" customWidth="1"/>
+    <col width="23.1" min="3" max="3" bestFit="1" customWidth="1"/>
     <col width="24.200000000000003" min="4" max="4" bestFit="1" customWidth="1"/>
     <col width="24.200000000000003" min="5" max="5" bestFit="1" customWidth="1"/>
     <col width="24.200000000000003" min="6" max="6" bestFit="1" customWidth="1"/>
-    <col width="25.3" min="7" max="7" bestFit="1" customWidth="1"/>
-    <col width="25.3" min="8" max="8" bestFit="1" customWidth="1"/>
-    <col width="25.3" min="9" max="9" bestFit="1" customWidth="1"/>
-    <col width="25.3" min="10" max="10" bestFit="1" customWidth="1"/>
+    <col width="24.200000000000003" min="7" max="7" bestFit="1" customWidth="1"/>
+    <col width="24.200000000000003" min="8" max="8" bestFit="1" customWidth="1"/>
+    <col width="24.200000000000003" min="9" max="9" bestFit="1" customWidth="1"/>
+    <col width="24.200000000000003" min="10" max="10" bestFit="1" customWidth="1"/>
     <col width="24.200000000000003" min="11" max="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -356,28 +356,28 @@
         <v>1.0</v>
       </c>
       <c r="D1" s="0" t="n">
-        <v>0.8777777777777778</v>
+        <v>0.9388888888888889</v>
       </c>
       <c r="E1" s="0" t="n">
-        <v>0.8777777777777778</v>
+        <v>0.9388888888888889</v>
       </c>
       <c r="F1" s="0" t="n">
-        <v>0.8777777777777778</v>
+        <v>0.9388888888888889</v>
       </c>
       <c r="G1" s="0" t="n">
-        <v>0.8777777777777778</v>
+        <v>0.9388888888888889</v>
       </c>
       <c r="H1" s="0" t="n">
-        <v>0.8777777777777778</v>
+        <v>0.9388888888888889</v>
       </c>
       <c r="I1" s="0" t="n">
-        <v>0.8777777777777778</v>
+        <v>0.9388888888888889</v>
       </c>
       <c r="J1" s="0" t="n">
-        <v>0.8777777777777778</v>
+        <v>0.9388888888888889</v>
       </c>
       <c r="K1" s="0" t="n">
-        <v>0.8777777777777778</v>
+        <v>0.9388888888888889</v>
       </c>
     </row>
     <row r="2">
@@ -387,34 +387,34 @@
         </is>
       </c>
       <c r="B2" s="0" t="n">
-        <v>0.24444444444444438</v>
+        <v>0.6222222222222222</v>
       </c>
       <c r="C2" s="0" t="n">
-        <v>0.20952380952380947</v>
+        <v>0.6047619047619047</v>
       </c>
       <c r="D2" s="0" t="n">
-        <v>0.1952380952380952</v>
+        <v>0.5976190476190476</v>
       </c>
       <c r="E2" s="0" t="n">
-        <v>0.1952380952380952</v>
+        <v>0.5976190476190476</v>
       </c>
       <c r="F2" s="0" t="n">
-        <v>0.1952380952380952</v>
+        <v>0.5976190476190476</v>
       </c>
       <c r="G2" s="0" t="n">
-        <v>0.1952380952380952</v>
+        <v>0.5653609831029186</v>
       </c>
       <c r="H2" s="0" t="n">
-        <v>0.17142857142857143</v>
+        <v>0.553968253968254</v>
       </c>
       <c r="I2" s="0" t="n">
-        <v>0.11666666666666667</v>
+        <v>0.5275641025641026</v>
       </c>
       <c r="J2" s="0" t="n">
-        <v>0.18095238095238095</v>
+        <v>0.5582181259600615</v>
       </c>
       <c r="K2" s="0" t="n">
-        <v>0.18095238095238095</v>
+        <v>0.5576893052302888</v>
       </c>
     </row>
     <row r="3">
@@ -424,34 +424,34 @@
         </is>
       </c>
       <c r="B3" s="0" t="n">
-        <v>0.5234126984126983</v>
+        <v>0.7617063492063492</v>
       </c>
       <c r="C3" s="0" t="n">
-        <v>0.5303350970017636</v>
+        <v>0.7405773845664556</v>
       </c>
       <c r="D3" s="0" t="n">
-        <v>0.251984126984127</v>
+        <v>0.581547619047619</v>
       </c>
       <c r="E3" s="0" t="n">
-        <v>0.251984126984127</v>
+        <v>0.5562246216315984</v>
       </c>
       <c r="F3" s="0" t="n">
-        <v>0.251984126984127</v>
+        <v>0.5562246216315984</v>
       </c>
       <c r="G3" s="0" t="n">
-        <v>0.251984126984127</v>
+        <v>0.5562246216315984</v>
       </c>
       <c r="H3" s="0" t="n">
-        <v>0.251984126984127</v>
+        <v>0.5562246216315984</v>
       </c>
       <c r="I3" s="0" t="n">
-        <v>0.251984126984127</v>
+        <v>0.5562246216315984</v>
       </c>
       <c r="J3" s="0" t="n">
-        <v>0.251984126984127</v>
+        <v>0.5562246216315984</v>
       </c>
       <c r="K3" s="0" t="n">
-        <v>0.2236111111111111</v>
+        <v>0.5436237373737374</v>
       </c>
     </row>
     <row r="4">
@@ -461,34 +461,34 @@
         </is>
       </c>
       <c r="B4" s="0" t="n">
-        <v>1.0</v>
+        <v>0.9883720930232558</v>
       </c>
       <c r="C4" s="0" t="n">
-        <v>0.17671957671957678</v>
+        <v>0.5564448947427671</v>
       </c>
       <c r="D4" s="0" t="n">
-        <v>0.19047619047619047</v>
+        <v>0.5560224089635855</v>
       </c>
       <c r="E4" s="0" t="n">
-        <v>0.17992424242424243</v>
+        <v>0.5600601035868893</v>
       </c>
       <c r="F4" s="0" t="n">
-        <v>0.2518518518518519</v>
+        <v>0.6055177626606199</v>
       </c>
       <c r="G4" s="0" t="n">
-        <v>0.16931216931216936</v>
+        <v>0.5301106301106301</v>
       </c>
       <c r="H4" s="0" t="n">
-        <v>0.10601469237832874</v>
+        <v>0.47608426926608743</v>
       </c>
       <c r="I4" s="0" t="n">
-        <v>0.086991711991712</v>
+        <v>0.443495855995856</v>
       </c>
       <c r="J4" s="0" t="n">
-        <v>0.06674718196457327</v>
+        <v>0.4084680056812342</v>
       </c>
       <c r="K4" s="0" t="n">
-        <v>0.12654320987654322</v>
+        <v>0.49508978675645343</v>
       </c>
     </row>
     <row r="5">
@@ -519,13 +519,13 @@
         <v>1.0</v>
       </c>
       <c r="I5" s="0" t="n">
-        <v>0.5</v>
+        <v>0.6944444444444444</v>
       </c>
       <c r="J5" s="0" t="n">
-        <v>0.5</v>
+        <v>0.6944444444444444</v>
       </c>
       <c r="K5" s="0" t="n">
-        <v>0.4285714285714286</v>
+        <v>0.6616541353383458</v>
       </c>
     </row>
     <row r="6">
@@ -535,34 +535,34 @@
         </is>
       </c>
       <c r="B6" s="0" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.9166666666666667</v>
       </c>
       <c r="C6" s="0" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.9166666666666667</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.9166666666666667</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.9166666666666667</v>
       </c>
       <c r="F6" s="0" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.9166666666666667</v>
       </c>
       <c r="G6" s="0" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.9166666666666667</v>
       </c>
       <c r="H6" s="0" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.9166666666666667</v>
       </c>
       <c r="I6" s="0" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.9166666666666667</v>
       </c>
       <c r="J6" s="0" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.9166666666666667</v>
       </c>
       <c r="K6" s="0" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.9166666666666667</v>
       </c>
     </row>
     <row r="7">
@@ -572,34 +572,34 @@
         </is>
       </c>
       <c r="B7" s="0" t="n">
-        <v>0.10069444444444445</v>
+        <v>0.5503472222222222</v>
       </c>
       <c r="C7" s="0" t="n">
-        <v>0.1284722222222222</v>
+        <v>0.5642361111111112</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>0.1284722222222222</v>
+        <v>0.5642361111111112</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>0.1284722222222222</v>
+        <v>0.5642361111111112</v>
       </c>
       <c r="F7" s="0" t="n">
-        <v>0.1284722222222222</v>
+        <v>0.5642361111111112</v>
       </c>
       <c r="G7" s="0" t="n">
-        <v>0.1284722222222222</v>
+        <v>0.5642361111111112</v>
       </c>
       <c r="H7" s="0" t="n">
-        <v>0.12251984126984128</v>
+        <v>0.5612599206349207</v>
       </c>
       <c r="I7" s="0" t="n">
-        <v>0.12251984126984128</v>
+        <v>0.5612599206349207</v>
       </c>
       <c r="J7" s="0" t="n">
-        <v>0.12251984126984128</v>
+        <v>0.5612599206349207</v>
       </c>
       <c r="K7" s="0" t="n">
-        <v>0.12251984126984128</v>
+        <v>0.5612599206349207</v>
       </c>
     </row>
     <row r="8">
@@ -609,34 +609,34 @@
         </is>
       </c>
       <c r="B8" s="0" t="n">
-        <v>0.22488095238095235</v>
+        <v>0.571624149659864</v>
       </c>
       <c r="C8" s="0" t="n">
-        <v>0.1494047619047619</v>
+        <v>0.5032738095238095</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>0.01911683277962347</v>
+        <v>0.35839562569213734</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>0.03434523809523809</v>
+        <v>0.3589447709463532</v>
       </c>
       <c r="F8" s="0" t="n">
-        <v>0.06730158730158729</v>
+        <v>0.41826617826617823</v>
       </c>
       <c r="G8" s="0" t="n">
-        <v>0.01256533101045296</v>
+        <v>0.322072139189437</v>
       </c>
       <c r="H8" s="0" t="n">
-        <v>0.052083333333333336</v>
+        <v>0.40839460784313725</v>
       </c>
       <c r="I8" s="0" t="n">
-        <v>0.052083333333333336</v>
+        <v>0.40839460784313725</v>
       </c>
       <c r="J8" s="0" t="n">
-        <v>0.052083333333333336</v>
+        <v>0.40839460784313725</v>
       </c>
       <c r="K8" s="0" t="n">
-        <v>0.0</v>
+        <v>0.38235294117647056</v>
       </c>
     </row>
     <row r="9">
@@ -646,34 +646,34 @@
         </is>
       </c>
       <c r="B9" s="0" t="n">
-        <v>0.6606060606060605</v>
+        <v>0.8204991087344028</v>
       </c>
       <c r="C9" s="0" t="n">
-        <v>0.6038567493112947</v>
+        <v>0.77465564738292</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>0.04798807749627421</v>
+        <v>0.4417155577354789</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>0.04646464646464646</v>
+        <v>0.41479858829256416</v>
       </c>
       <c r="F9" s="0" t="n">
-        <v>0.06209790209790209</v>
+        <v>0.42688228438228437</v>
       </c>
       <c r="G9" s="0" t="n">
-        <v>0.042045454545454546</v>
+        <v>0.4041396103896104</v>
       </c>
       <c r="H9" s="0" t="n">
-        <v>0.11098484848484849</v>
+        <v>0.411814263322884</v>
       </c>
       <c r="I9" s="0" t="n">
-        <v>0.1373986013986014</v>
+        <v>0.422032634032634</v>
       </c>
       <c r="J9" s="0" t="n">
-        <v>0.14798951048951048</v>
+        <v>0.4438577689433854</v>
       </c>
       <c r="K9" s="0" t="n">
-        <v>0.06108452950558213</v>
+        <v>0.39467269953539974</v>
       </c>
     </row>
     <row r="10">
@@ -683,34 +683,34 @@
         </is>
       </c>
       <c r="B10" s="0" t="n">
-        <v>0.2293956043956044</v>
+        <v>0.487146781789639</v>
       </c>
       <c r="C10" s="0" t="n">
-        <v>0.19012605042016806</v>
+        <v>0.5138130252100841</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>0.08605571016285304</v>
+        <v>0.44664231291275186</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>0.08010243724529441</v>
+        <v>0.45959144850770467</v>
       </c>
       <c r="F10" s="0" t="n">
-        <v>0.03280730897009967</v>
+        <v>0.34198504983388706</v>
       </c>
       <c r="G10" s="0" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.41025641025641024</v>
       </c>
       <c r="H10" s="0" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.37629937629937626</v>
       </c>
       <c r="I10" s="0" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.37629937629937626</v>
       </c>
       <c r="J10" s="0" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.37629937629937626</v>
       </c>
       <c r="K10" s="0" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.37629937629937626</v>
       </c>
     </row>
     <row r="11">
@@ -720,34 +720,34 @@
         </is>
       </c>
       <c r="B11" s="0" t="n">
-        <v>0.3619318181818182</v>
+        <v>0.6254103535353535</v>
       </c>
       <c r="C11" s="0" t="n">
-        <v>0.2995867768595041</v>
+        <v>0.5432360113805716</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>0.11474116161616163</v>
+        <v>0.3780227547211243</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>0.28814935064935066</v>
+        <v>0.48966291061879297</v>
       </c>
       <c r="F11" s="0" t="n">
-        <v>0.04512987012987013</v>
+        <v>0.37256493506493504</v>
       </c>
       <c r="G11" s="0" t="n">
-        <v>0.04512987012987013</v>
+        <v>0.37256493506493504</v>
       </c>
       <c r="H11" s="0" t="n">
-        <v>0.04512987012987013</v>
+        <v>0.37256493506493504</v>
       </c>
       <c r="I11" s="0" t="n">
-        <v>0.04512987012987013</v>
+        <v>0.3807738902888157</v>
       </c>
       <c r="J11" s="0" t="n">
-        <v>0.28701298701298705</v>
+        <v>0.4995670995670996</v>
       </c>
       <c r="K11" s="0" t="n">
-        <v>0.32613636363636367</v>
+        <v>0.5191287878787879</v>
       </c>
     </row>
     <row r="12">
@@ -760,31 +760,31 @@
         <v>1.0</v>
       </c>
       <c r="C12" s="0" t="n">
-        <v>0.11312499999999996</v>
+        <v>0.5117863805970149</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>0.11312499999999996</v>
+        <v>0.5275769927536231</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>0.1436805555555555</v>
+        <v>0.5448132507507507</v>
       </c>
       <c r="F12" s="0" t="n">
-        <v>0.263611111111111</v>
+        <v>0.6036365414710485</v>
       </c>
       <c r="G12" s="0" t="n">
-        <v>0.03121527777777778</v>
+        <v>0.4230150462962963</v>
       </c>
       <c r="H12" s="0" t="n">
-        <v>0.03121527777777778</v>
+        <v>0.40022302350427347</v>
       </c>
       <c r="I12" s="0" t="n">
-        <v>0.03121527777777778</v>
+        <v>0.40022302350427347</v>
       </c>
       <c r="J12" s="0" t="n">
-        <v>0.03121527777777778</v>
+        <v>0.40022302350427347</v>
       </c>
       <c r="K12" s="0" t="n">
-        <v>0.03121527777777778</v>
+        <v>0.40022302350427347</v>
       </c>
     </row>
     <row r="13">
@@ -794,34 +794,34 @@
         </is>
       </c>
       <c r="B13" s="0" t="n">
-        <v>0.6</v>
+        <v>0.6269230769230769</v>
       </c>
       <c r="C13" s="0" t="n">
-        <v>0.0967741935483871</v>
+        <v>0.419815668202765</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>0.03409090909090909</v>
+        <v>0.24932891911238364</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>0.375</v>
+        <v>0.5056818181818181</v>
       </c>
       <c r="F13" s="0" t="n">
-        <v>0.375</v>
+        <v>0.5056818181818181</v>
       </c>
       <c r="G13" s="0" t="n">
-        <v>0.125</v>
+        <v>0.3806818181818182</v>
       </c>
       <c r="H13" s="0" t="n">
-        <v>0.375</v>
+        <v>0.49702380952380953</v>
       </c>
       <c r="I13" s="0" t="n">
-        <v>0.375</v>
+        <v>0.49702380952380953</v>
       </c>
       <c r="J13" s="0" t="n">
-        <v>0.375</v>
+        <v>0.5056818181818181</v>
       </c>
       <c r="K13" s="0" t="n">
-        <v>0.375</v>
+        <v>0.5056818181818181</v>
       </c>
     </row>
     <row r="14">
@@ -831,34 +831,34 @@
         </is>
       </c>
       <c r="B14" s="0" t="n">
-        <v>0.48958333333333337</v>
+        <v>0.7009320175438596</v>
       </c>
       <c r="C14" s="0" t="n">
-        <v>0.3397129186602871</v>
+        <v>0.5571804029921154</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>0.03905380333951763</v>
+        <v>0.35452690166975875</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>0.04166666666666667</v>
+        <v>0.3639705882352941</v>
       </c>
       <c r="F14" s="0" t="n">
-        <v>0.10606060606060608</v>
+        <v>0.4761072261072261</v>
       </c>
       <c r="G14" s="0" t="n">
-        <v>0.10606060606060608</v>
+        <v>0.4574420677361854</v>
       </c>
       <c r="H14" s="0" t="n">
-        <v>0.10606060606060608</v>
+        <v>0.4772727272727273</v>
       </c>
       <c r="I14" s="0" t="n">
-        <v>0.017587939698492466</v>
+        <v>0.34365635517034715</v>
       </c>
       <c r="J14" s="0" t="n">
-        <v>0.3111111111111111</v>
+        <v>0.5841269841269842</v>
       </c>
       <c r="K14" s="0" t="n">
-        <v>0.3111111111111111</v>
+        <v>0.5841269841269842</v>
       </c>
     </row>
     <row r="15">

--- a/all_sim/gpt_realset.xlsx
+++ b/all_sim/gpt_realset.xlsx
@@ -331,16 +331,16 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
     <col width="17.6" min="1" max="1" bestFit="1" customWidth="1"/>
-    <col width="23.1" min="2" max="2" bestFit="1" customWidth="1"/>
-    <col width="23.1" min="3" max="3" bestFit="1" customWidth="1"/>
-    <col width="24.200000000000003" min="4" max="4" bestFit="1" customWidth="1"/>
-    <col width="24.200000000000003" min="5" max="5" bestFit="1" customWidth="1"/>
-    <col width="24.200000000000003" min="6" max="6" bestFit="1" customWidth="1"/>
-    <col width="24.200000000000003" min="7" max="7" bestFit="1" customWidth="1"/>
-    <col width="24.200000000000003" min="8" max="8" bestFit="1" customWidth="1"/>
-    <col width="24.200000000000003" min="9" max="9" bestFit="1" customWidth="1"/>
-    <col width="24.200000000000003" min="10" max="10" bestFit="1" customWidth="1"/>
-    <col width="24.200000000000003" min="11" max="11" bestFit="1" customWidth="1"/>
+    <col width="24.200000000000003" min="2" max="2" bestFit="1" customWidth="1"/>
+    <col width="24.200000000000003" min="3" max="3" bestFit="1" customWidth="1"/>
+    <col width="25.3" min="4" max="4" bestFit="1" customWidth="1"/>
+    <col width="25.3" min="5" max="5" bestFit="1" customWidth="1"/>
+    <col width="25.3" min="6" max="6" bestFit="1" customWidth="1"/>
+    <col width="25.3" min="7" max="7" bestFit="1" customWidth="1"/>
+    <col width="25.3" min="8" max="8" bestFit="1" customWidth="1"/>
+    <col width="25.3" min="9" max="9" bestFit="1" customWidth="1"/>
+    <col width="25.3" min="10" max="10" bestFit="1" customWidth="1"/>
+    <col width="25.3" min="11" max="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -356,28 +356,28 @@
         <v>1.0</v>
       </c>
       <c r="D1" s="0" t="n">
-        <v>0.9388888888888889</v>
+        <v>0.8777777777777778</v>
       </c>
       <c r="E1" s="0" t="n">
-        <v>0.9388888888888889</v>
+        <v>0.8777777777777778</v>
       </c>
       <c r="F1" s="0" t="n">
-        <v>0.9388888888888889</v>
+        <v>0.8777777777777778</v>
       </c>
       <c r="G1" s="0" t="n">
-        <v>0.9388888888888889</v>
+        <v>0.8777777777777778</v>
       </c>
       <c r="H1" s="0" t="n">
-        <v>0.9388888888888889</v>
+        <v>0.8777777777777778</v>
       </c>
       <c r="I1" s="0" t="n">
-        <v>0.9388888888888889</v>
+        <v>0.8777777777777778</v>
       </c>
       <c r="J1" s="0" t="n">
-        <v>0.9388888888888889</v>
+        <v>0.8777777777777778</v>
       </c>
       <c r="K1" s="0" t="n">
-        <v>0.9388888888888889</v>
+        <v>0.8777777777777778</v>
       </c>
     </row>
     <row r="2">
@@ -387,34 +387,34 @@
         </is>
       </c>
       <c r="B2" s="0" t="n">
-        <v>0.6222222222222222</v>
+        <v>0.24444444444444438</v>
       </c>
       <c r="C2" s="0" t="n">
-        <v>0.6047619047619047</v>
+        <v>0.20952380952380947</v>
       </c>
       <c r="D2" s="0" t="n">
-        <v>0.5976190476190476</v>
+        <v>0.1952380952380952</v>
       </c>
       <c r="E2" s="0" t="n">
-        <v>0.5976190476190476</v>
+        <v>0.1952380952380952</v>
       </c>
       <c r="F2" s="0" t="n">
-        <v>0.5976190476190476</v>
+        <v>0.1952380952380952</v>
       </c>
       <c r="G2" s="0" t="n">
-        <v>0.5653609831029186</v>
+        <v>0.18264208909370197</v>
       </c>
       <c r="H2" s="0" t="n">
-        <v>0.553968253968254</v>
+        <v>0.16054421768707483</v>
       </c>
       <c r="I2" s="0" t="n">
-        <v>0.5275641025641026</v>
+        <v>0.1094871794871795</v>
       </c>
       <c r="J2" s="0" t="n">
-        <v>0.5582181259600615</v>
+        <v>0.16927803379416284</v>
       </c>
       <c r="K2" s="0" t="n">
-        <v>0.5576893052302888</v>
+        <v>0.16908665105386417</v>
       </c>
     </row>
     <row r="3">
@@ -424,34 +424,34 @@
         </is>
       </c>
       <c r="B3" s="0" t="n">
-        <v>0.7617063492063492</v>
+        <v>0.5234126984126983</v>
       </c>
       <c r="C3" s="0" t="n">
-        <v>0.7405773845664556</v>
+        <v>0.5042530430508572</v>
       </c>
       <c r="D3" s="0" t="n">
-        <v>0.581547619047619</v>
+        <v>0.22958553791887124</v>
       </c>
       <c r="E3" s="0" t="n">
-        <v>0.5562246216315984</v>
+        <v>0.2168235511258767</v>
       </c>
       <c r="F3" s="0" t="n">
-        <v>0.5562246216315984</v>
+        <v>0.2168235511258767</v>
       </c>
       <c r="G3" s="0" t="n">
-        <v>0.5562246216315984</v>
+        <v>0.2168235511258767</v>
       </c>
       <c r="H3" s="0" t="n">
-        <v>0.5562246216315984</v>
+        <v>0.2168235511258767</v>
       </c>
       <c r="I3" s="0" t="n">
-        <v>0.5562246216315984</v>
+        <v>0.2168235511258767</v>
       </c>
       <c r="J3" s="0" t="n">
-        <v>0.5562246216315984</v>
+        <v>0.2168235511258767</v>
       </c>
       <c r="K3" s="0" t="n">
-        <v>0.5436237373737374</v>
+        <v>0.19311868686868686</v>
       </c>
     </row>
     <row r="4">
@@ -461,34 +461,34 @@
         </is>
       </c>
       <c r="B4" s="0" t="n">
-        <v>0.9883720930232558</v>
+        <v>0.9767441860465116</v>
       </c>
       <c r="C4" s="0" t="n">
-        <v>0.5564448947427671</v>
+        <v>0.16543960373747613</v>
       </c>
       <c r="D4" s="0" t="n">
-        <v>0.5560224089635855</v>
+        <v>0.17553688141923438</v>
       </c>
       <c r="E4" s="0" t="n">
-        <v>0.5600601035868893</v>
+        <v>0.17024196042053188</v>
       </c>
       <c r="F4" s="0" t="n">
-        <v>0.6055177626606199</v>
+        <v>0.2415721844293273</v>
       </c>
       <c r="G4" s="0" t="n">
-        <v>0.5301106301106301</v>
+        <v>0.1508417508417509</v>
       </c>
       <c r="H4" s="0" t="n">
-        <v>0.47608426926608743</v>
+        <v>0.0897047397047397</v>
       </c>
       <c r="I4" s="0" t="n">
-        <v>0.443495855995856</v>
+        <v>0.0695933695933696</v>
       </c>
       <c r="J4" s="0" t="n">
-        <v>0.4084680056812342</v>
+        <v>0.05380703426494361</v>
       </c>
       <c r="K4" s="0" t="n">
-        <v>0.49508978675645343</v>
+        <v>0.10928731762065096</v>
       </c>
     </row>
     <row r="5">
@@ -519,13 +519,13 @@
         <v>1.0</v>
       </c>
       <c r="I5" s="0" t="n">
-        <v>0.6944444444444444</v>
+        <v>0.4444444444444444</v>
       </c>
       <c r="J5" s="0" t="n">
-        <v>0.6944444444444444</v>
+        <v>0.4444444444444444</v>
       </c>
       <c r="K5" s="0" t="n">
-        <v>0.6616541353383458</v>
+        <v>0.3834586466165414</v>
       </c>
     </row>
     <row r="6">
@@ -535,34 +535,34 @@
         </is>
       </c>
       <c r="B6" s="0" t="n">
-        <v>0.9166666666666667</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="C6" s="0" t="n">
-        <v>0.9166666666666667</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>0.9166666666666667</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>0.9166666666666667</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="F6" s="0" t="n">
-        <v>0.9166666666666667</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="G6" s="0" t="n">
-        <v>0.9166666666666667</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="H6" s="0" t="n">
-        <v>0.9166666666666667</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="I6" s="0" t="n">
-        <v>0.9166666666666667</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="J6" s="0" t="n">
-        <v>0.9166666666666667</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="K6" s="0" t="n">
-        <v>0.9166666666666667</v>
+        <v>0.8333333333333334</v>
       </c>
     </row>
     <row r="7">
@@ -572,34 +572,34 @@
         </is>
       </c>
       <c r="B7" s="0" t="n">
-        <v>0.5503472222222222</v>
+        <v>0.10069444444444445</v>
       </c>
       <c r="C7" s="0" t="n">
-        <v>0.5642361111111112</v>
+        <v>0.1284722222222222</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>0.5642361111111112</v>
+        <v>0.1284722222222222</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>0.5642361111111112</v>
+        <v>0.1284722222222222</v>
       </c>
       <c r="F7" s="0" t="n">
-        <v>0.5642361111111112</v>
+        <v>0.1284722222222222</v>
       </c>
       <c r="G7" s="0" t="n">
-        <v>0.5642361111111112</v>
+        <v>0.1284722222222222</v>
       </c>
       <c r="H7" s="0" t="n">
-        <v>0.5612599206349207</v>
+        <v>0.12251984126984128</v>
       </c>
       <c r="I7" s="0" t="n">
-        <v>0.5612599206349207</v>
+        <v>0.12251984126984128</v>
       </c>
       <c r="J7" s="0" t="n">
-        <v>0.5612599206349207</v>
+        <v>0.12251984126984128</v>
       </c>
       <c r="K7" s="0" t="n">
-        <v>0.5612599206349207</v>
+        <v>0.12251984126984128</v>
       </c>
     </row>
     <row r="8">
@@ -609,34 +609,34 @@
         </is>
       </c>
       <c r="B8" s="0" t="n">
-        <v>0.571624149659864</v>
+        <v>0.20652332361516032</v>
       </c>
       <c r="C8" s="0" t="n">
-        <v>0.5032738095238095</v>
+        <v>0.12806122448979593</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>0.35839562569213734</v>
+        <v>0.013337325195086142</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>0.3589447709463532</v>
+        <v>0.023476491862567807</v>
       </c>
       <c r="F8" s="0" t="n">
-        <v>0.41826617826617823</v>
+        <v>0.05177045177045176</v>
       </c>
       <c r="G8" s="0" t="n">
-        <v>0.322072139189437</v>
+        <v>0.00793599853291766</v>
       </c>
       <c r="H8" s="0" t="n">
-        <v>0.40839460784313725</v>
+        <v>0.03982843137254902</v>
       </c>
       <c r="I8" s="0" t="n">
-        <v>0.40839460784313725</v>
+        <v>0.03982843137254902</v>
       </c>
       <c r="J8" s="0" t="n">
-        <v>0.40839460784313725</v>
+        <v>0.03982843137254902</v>
       </c>
       <c r="K8" s="0" t="n">
-        <v>0.38235294117647056</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="9">
@@ -646,34 +646,34 @@
         </is>
       </c>
       <c r="B9" s="0" t="n">
-        <v>0.8204991087344028</v>
+        <v>0.647653000594177</v>
       </c>
       <c r="C9" s="0" t="n">
-        <v>0.77465564738292</v>
+        <v>0.5709191084397696</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>0.4417155577354789</v>
+        <v>0.040091305250051876</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>0.41479858829256416</v>
+        <v>0.03638797614701229</v>
       </c>
       <c r="F9" s="0" t="n">
-        <v>0.42688228438228437</v>
+        <v>0.04916083916083915</v>
       </c>
       <c r="G9" s="0" t="n">
-        <v>0.4041396103896104</v>
+        <v>0.032216646989374265</v>
       </c>
       <c r="H9" s="0" t="n">
-        <v>0.411814263322884</v>
+        <v>0.07909265064437479</v>
       </c>
       <c r="I9" s="0" t="n">
-        <v>0.422032634032634</v>
+        <v>0.09709501165501166</v>
       </c>
       <c r="J9" s="0" t="n">
-        <v>0.4438577689433854</v>
+        <v>0.10947169269087077</v>
       </c>
       <c r="K9" s="0" t="n">
-        <v>0.39467269953539974</v>
+        <v>0.044485472574717425</v>
       </c>
     </row>
     <row r="10">
@@ -683,34 +683,34 @@
         </is>
       </c>
       <c r="B10" s="0" t="n">
-        <v>0.487146781789639</v>
+        <v>0.17087631755999105</v>
       </c>
       <c r="C10" s="0" t="n">
-        <v>0.5138130252100841</v>
+        <v>0.15923056722689075</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>0.44664231291275186</v>
+        <v>0.0694666576013392</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>0.45959144850770467</v>
+        <v>0.06721238987248841</v>
       </c>
       <c r="F10" s="0" t="n">
-        <v>0.34198504983388706</v>
+        <v>0.021362898864250947</v>
       </c>
       <c r="G10" s="0" t="n">
-        <v>0.41025641025641024</v>
+        <v>0.0571992110453649</v>
       </c>
       <c r="H10" s="0" t="n">
-        <v>0.37629937629937626</v>
+        <v>0.05197505197505198</v>
       </c>
       <c r="I10" s="0" t="n">
-        <v>0.37629937629937626</v>
+        <v>0.05197505197505198</v>
       </c>
       <c r="J10" s="0" t="n">
-        <v>0.37629937629937626</v>
+        <v>0.05197505197505198</v>
       </c>
       <c r="K10" s="0" t="n">
-        <v>0.37629937629937626</v>
+        <v>0.05197505197505198</v>
       </c>
     </row>
     <row r="11">
@@ -720,34 +720,34 @@
         </is>
       </c>
       <c r="B11" s="0" t="n">
-        <v>0.6254103535353535</v>
+        <v>0.3217171717171717</v>
       </c>
       <c r="C11" s="0" t="n">
-        <v>0.5432360113805716</v>
+        <v>0.23574041457797043</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>0.3780227547211243</v>
+        <v>0.07358400581906017</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>0.48966291061879297</v>
+        <v>0.19916205118411</v>
       </c>
       <c r="F11" s="0" t="n">
-        <v>0.37256493506493504</v>
+        <v>0.03159090909090909</v>
       </c>
       <c r="G11" s="0" t="n">
-        <v>0.37256493506493504</v>
+        <v>0.03159090909090909</v>
       </c>
       <c r="H11" s="0" t="n">
-        <v>0.37256493506493504</v>
+        <v>0.03159090909090909</v>
       </c>
       <c r="I11" s="0" t="n">
-        <v>0.3807738902888157</v>
+        <v>0.032331847257220395</v>
       </c>
       <c r="J11" s="0" t="n">
-        <v>0.4995670995670996</v>
+        <v>0.20438803620621807</v>
       </c>
       <c r="K11" s="0" t="n">
-        <v>0.5191287878787879</v>
+        <v>0.23224862258953172</v>
       </c>
     </row>
     <row r="12">
@@ -760,31 +760,31 @@
         <v>1.0</v>
       </c>
       <c r="C12" s="0" t="n">
-        <v>0.5117863805970149</v>
+        <v>0.10299440298507459</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>0.5275769927536231</v>
+        <v>0.10656702898550721</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>0.5448132507507507</v>
+        <v>0.13591403903903898</v>
       </c>
       <c r="F12" s="0" t="n">
-        <v>0.6036365414710485</v>
+        <v>0.24875978090766812</v>
       </c>
       <c r="G12" s="0" t="n">
-        <v>0.4230150462962963</v>
+        <v>0.025434670781893008</v>
       </c>
       <c r="H12" s="0" t="n">
-        <v>0.40022302350427347</v>
+        <v>0.024011752136752135</v>
       </c>
       <c r="I12" s="0" t="n">
-        <v>0.40022302350427347</v>
+        <v>0.024011752136752135</v>
       </c>
       <c r="J12" s="0" t="n">
-        <v>0.40022302350427347</v>
+        <v>0.024011752136752135</v>
       </c>
       <c r="K12" s="0" t="n">
-        <v>0.40022302350427347</v>
+        <v>0.024011752136752135</v>
       </c>
     </row>
     <row r="13">
@@ -794,34 +794,34 @@
         </is>
       </c>
       <c r="B13" s="0" t="n">
-        <v>0.6269230769230769</v>
+        <v>0.3923076923076923</v>
       </c>
       <c r="C13" s="0" t="n">
-        <v>0.419815668202765</v>
+        <v>0.07188940092165899</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>0.24932891911238364</v>
+        <v>0.015837508947745164</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>0.5056818181818181</v>
+        <v>0.23863636363636365</v>
       </c>
       <c r="F13" s="0" t="n">
-        <v>0.5056818181818181</v>
+        <v>0.23863636363636365</v>
       </c>
       <c r="G13" s="0" t="n">
-        <v>0.3806818181818182</v>
+        <v>0.07954545454545454</v>
       </c>
       <c r="H13" s="0" t="n">
-        <v>0.49702380952380953</v>
+        <v>0.23214285714285715</v>
       </c>
       <c r="I13" s="0" t="n">
-        <v>0.49702380952380953</v>
+        <v>0.23214285714285715</v>
       </c>
       <c r="J13" s="0" t="n">
-        <v>0.5056818181818181</v>
+        <v>0.23863636363636365</v>
       </c>
       <c r="K13" s="0" t="n">
-        <v>0.5056818181818181</v>
+        <v>0.23863636363636365</v>
       </c>
     </row>
     <row r="14">
@@ -831,34 +831,34 @@
         </is>
       </c>
       <c r="B14" s="0" t="n">
-        <v>0.7009320175438596</v>
+        <v>0.4466374269005848</v>
       </c>
       <c r="C14" s="0" t="n">
-        <v>0.5571804029921154</v>
+        <v>0.2631578947368421</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>0.35452690166975875</v>
+        <v>0.026166048237476806</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>0.3639705882352941</v>
+        <v>0.028594771241830068</v>
       </c>
       <c r="F14" s="0" t="n">
-        <v>0.4761072261072261</v>
+        <v>0.08974358974358976</v>
       </c>
       <c r="G14" s="0" t="n">
-        <v>0.4574420677361854</v>
+        <v>0.08578431372549021</v>
       </c>
       <c r="H14" s="0" t="n">
-        <v>0.4772727272727273</v>
+        <v>0.08999081726354455</v>
       </c>
       <c r="I14" s="0" t="n">
-        <v>0.34365635517034715</v>
+        <v>0.011779078880641742</v>
       </c>
       <c r="J14" s="0" t="n">
-        <v>0.5841269841269842</v>
+        <v>0.26666666666666666</v>
       </c>
       <c r="K14" s="0" t="n">
-        <v>0.5841269841269842</v>
+        <v>0.26666666666666666</v>
       </c>
     </row>
     <row r="15">
